--- a/doc/Exemple Importation/template_entretiens_historique_exemple.xlsx
+++ b/doc/Exemple Importation/template_entretiens_historique_exemple.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D999"/>
+  <dimension ref="A1:E999"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -462,7 +462,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Remplacez la/les ligne(s) d'exemple par vos données. La ligne d'explications (ligne 4) est indicative, à supprimer avant l'import. Le type d'entretien est choisi une fois pour tout le fichier au moment de l'import, pas dans une colonne.</t>
+          <t>Remplacez la/les ligne(s) d'exemple par vos données. La ligne d'explications (ligne 4) est indicative, à supprimer avant l'import. Le type d'entretien peut être renseigné par ligne (colonne Type Entretien) ou choisi une fois pour tout le fichier au moment de l'import si la colonne est vide.</t>
         </is>
       </c>
     </row>
@@ -487,6 +487,11 @@
           <t>Date de réalisation</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Type Entretien</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -509,6 +514,11 @@
           <t>Format JJ/MM/AAAA (optionnel)</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Entretien d'évaluation / Entretien professionnel / Entretien de bilan / Entretien forfait jours et charges / Entretien de fin de carrière (optionnel, sinon reprend le type choisi au moment de l'import)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -531,6 +541,11 @@
           <t>03/06/2024</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Entretien d'évaluation</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">

--- a/doc/Exemple Importation/template_entretiens_historique_exemple.xlsx
+++ b/doc/Exemple Importation/template_entretiens_historique_exemple.xlsx
@@ -462,7 +462,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Remplacez la/les ligne(s) d'exemple par vos données. La ligne d'explications (ligne 4) est indicative, à supprimer avant l'import. Le type d'entretien peut être renseigné par ligne (colonne Type Entretien) ou choisi une fois pour tout le fichier au moment de l'import si la colonne est vide.</t>
+          <t>Remplacez la/les ligne(s) d'exemple par vos données. La ligne d'explications (ligne 4) est indicative, à supprimer avant l'import.</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Entretien d'évaluation / Entretien professionnel / Entretien de bilan / Entretien forfait jours et charges / Entretien de fin de carrière (optionnel, sinon reprend le type choisi au moment de l'import)</t>
+          <t>Entretien d'évaluation / Entretien professionnel / Entretien de bilan / Entretien forfait jours et charges / Entretien de fin de carrière (obligatoire)</t>
         </is>
       </c>
     </row>

--- a/doc/Exemple Importation/template_entretiens_historique_exemple.xlsx
+++ b/doc/Exemple Importation/template_entretiens_historique_exemple.xlsx
@@ -568,6 +568,11 @@
           <t>05/09/2024</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Entretien professionnel</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
